--- a/Portal_Parceiros_Catedral.xlsx
+++ b/Portal_Parceiros_Catedral.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dejaime\Projetos_VSCode\parceirosnew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430CFC0A-BD06-4A34-A98A-98B073605509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFA023F-7630-4F1A-98AA-AB7F390A750C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{88F60E3E-25F4-44BD-B4F3-062C246B366D}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="34">
   <si>
     <t>Indicações</t>
   </si>
@@ -962,14 +962,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB31CB0-A0D2-436E-A799-A34B8BF364BE}">
-  <dimension ref="D4:G26"/>
+  <dimension ref="D4:F23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>0</v>
       </c>
@@ -980,7 +980,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="4:6" x14ac:dyDescent="0.3">
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
@@ -988,7 +988,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>1</v>
       </c>
@@ -999,7 +999,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="4:6" x14ac:dyDescent="0.3">
       <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>2</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="4:6" x14ac:dyDescent="0.3">
       <c r="E9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1026,60 +1026,60 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="4:6" x14ac:dyDescent="0.3">
       <c r="E11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="4:6" x14ac:dyDescent="0.3">
       <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="4:6" x14ac:dyDescent="0.3">
       <c r="E13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>3</v>
+      </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" t="s">
-        <v>3</v>
-      </c>
+    <row r="15" spans="4:6" x14ac:dyDescent="0.3">
       <c r="E15" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="4:6" x14ac:dyDescent="0.3">
       <c r="E16" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>29</v>
@@ -1087,73 +1087,65 @@
     </row>
     <row r="17" spans="4:6" x14ac:dyDescent="0.3">
       <c r="E17" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>4</v>
+      </c>
       <c r="E18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>29</v>
       </c>
     </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="20" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D20" t="s">
-        <v>4</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="21" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D21" t="s">
-        <v>5</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="E22" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="E23" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D25" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1" t="s">
         <v>29</v>
       </c>
     </row>
